--- a/public/images/category/pillows/Jala_Pillow_Catalog.xlsx
+++ b/public/images/category/pillows/Jala_Pillow_Catalog.xlsx
@@ -1,17 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Luxury\public\images\category\pillows\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C27C81B-D597-446A-8DB9-F34FBCD52A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Pillows" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Pillows" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -22,127 +38,126 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
   <si>
-    <t xml:space="preserve">SKU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Design</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Color</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Material</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regular Price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discount %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sale Price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Short Description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pillow-Molty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Molty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pillow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">White with Maroon Piping</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Premium Fiber Fill, Cotton Cover</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Molty Pillow brings back classic everyday comfort with its soft, generously filled fiber core wrapped in a smooth cotton-blend cover. Finished with a neat maroon piping edge, it offers gentle, consistent support for back and side sleepers alike, night after night.
+    <t>SKU</t>
+  </si>
+  <si>
+    <t>Product Name</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Design</t>
+  </si>
+  <si>
+    <t>Color</t>
+  </si>
+  <si>
+    <t>Material</t>
+  </si>
+  <si>
+    <t>Regular Price</t>
+  </si>
+  <si>
+    <t>Discount %</t>
+  </si>
+  <si>
+    <t>Sale Price</t>
+  </si>
+  <si>
+    <t>Stock</t>
+  </si>
+  <si>
+    <t>Short Description</t>
+  </si>
+  <si>
+    <t>Pillow-Molty</t>
+  </si>
+  <si>
+    <t>Molty</t>
+  </si>
+  <si>
+    <t>Pillow</t>
+  </si>
+  <si>
+    <t>Plain</t>
+  </si>
+  <si>
+    <t>White with Maroon Piping</t>
+  </si>
+  <si>
+    <t>Premium Fiber Fill, Cotton Cover</t>
+  </si>
+  <si>
+    <t>The Molty Pillow brings back classic everyday comfort with its soft, generously filled fiber core wrapped in a smooth cotton-blend cover. Finished with a neat maroon piping edge, it offers gentle, consistent support for back and side sleepers alike, night after night.
 Everyday softness with a classic, comfortable feel.</t>
   </si>
   <si>
-    <t xml:space="preserve">Pillow-C-Luxury Gel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C-Luxury Gel Pillow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cooling Gel Vent Panel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cooling Gel-Infused Fiber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The C-Luxury Gel Pillow is engineered for hot sleepers, featuring a breathable circular gel-vent panel that channels heat away and keeps the surface cool through the night. The vibrant red cover wraps a cooling gel-infused fiber fill that stays supportive without trapping warmth.
+    <t>Pillow-C-Luxury Gel</t>
+  </si>
+  <si>
+    <t>C-Luxury Gel Pillow</t>
+  </si>
+  <si>
+    <t>Cooling Gel Vent Panel</t>
+  </si>
+  <si>
+    <t>Red</t>
+  </si>
+  <si>
+    <t>Cooling Gel-Infused Fiber</t>
+  </si>
+  <si>
+    <t>The C-Luxury Gel Pillow is engineered for hot sleepers, featuring a breathable circular gel-vent panel that channels heat away and keeps the surface cool through the night. The vibrant red cover wraps a cooling gel-infused fiber fill that stays supportive without trapping warmth.
 Stay cool all night with breathable gel-vent comfort.</t>
   </si>
   <si>
-    <t xml:space="preserve">Pillow-Memory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Memory Pillow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contour Ergonomic Shape, Jacquard Floral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">White</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Memory Foam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Memory Pillow uses viscoelastic memory foam that responds to your body's warmth and weight, gradually molding to the shape of your head and neck, then slowly returning to its original form once you get up. Wrapped in a white jacquard floral cover, it offers a denser, more contoured feel than a standard fiber pillow. Every pillow is machine-made to the same precise shape for consistent quality across the batch.                                                                                                                       Slow-rebound memory foam that adapts to you, then bounces back.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pillow-C-Soyabean Fiber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C-Soyabean Fiber Pillow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diamond Quilted Stitch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">White with Gold Piping</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soyabean Fiber Fill, Quilted Cover</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The C-Soyabean Fiber Pillow elevates the everyday pillow with a plush diamond-quilted cover finished in crisp white with a warm gold piping trim. Filled with resilient soyabean fiber, it stays fluffy and supportive wash after wash, adding a touch of hotel-style luxury to any bed.
+    <t>Pillow-Memory</t>
+  </si>
+  <si>
+    <t>Memory Pillow</t>
+  </si>
+  <si>
+    <t>Contour Ergonomic Shape, Jacquard Floral</t>
+  </si>
+  <si>
+    <t>White</t>
+  </si>
+  <si>
+    <t>Memory Foam</t>
+  </si>
+  <si>
+    <t>The Memory Pillow uses viscoelastic memory foam that responds to your body's warmth and weight, gradually molding to the shape of your head and neck, then slowly returning to its original form once you get up. Wrapped in a white jacquard floral cover, it offers a denser, more contoured feel than a standard fiber pillow. Every pillow is machine-made to the same precise shape for consistent quality across the batch.                                                                                                                       Slow-rebound memory foam that adapts to you, then bounces back.</t>
+  </si>
+  <si>
+    <t>Pillow-C-Soyabean Fiber</t>
+  </si>
+  <si>
+    <t>C-Soyabean Fiber Pillow</t>
+  </si>
+  <si>
+    <t>Diamond Quilted Stitch</t>
+  </si>
+  <si>
+    <t>White with Gold Piping</t>
+  </si>
+  <si>
+    <t>Soyabean Fiber Fill, Quilted Cover</t>
+  </si>
+  <si>
+    <t>The C-Soyabean Fiber Pillow elevates the everyday pillow with a plush diamond-quilted cover finished in crisp white with a warm gold piping trim. Filled with resilient soyabean fiber, it stays fluffy and supportive wash after wash, adding a touch of hotel-style luxury to any bed.
 Plush soyabean fiber comfort with a touch of everyday luxury.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="&quot;Rs. &quot;#,##0"/>
-    <numFmt numFmtId="166" formatCode="0\%"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="&quot;Rs. &quot;#,##0"/>
+    <numFmt numFmtId="165" formatCode="0\%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -151,32 +166,15 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -195,14 +193,14 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFB7B7B7"/>
       </left>
@@ -218,65 +216,32 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -335,33 +300,361 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="55"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
+    <col min="6" max="6" width="26" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="10" customWidth="1"/>
+    <col min="11" max="11" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -396,7 +689,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
@@ -415,24 +708,24 @@
       <c r="F2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="3">
         <v>5500</v>
       </c>
-      <c r="H2" s="4" t="n">
-        <f aca="false">ROUND((G2-I2)/G2*100,0)</f>
+      <c r="H2" s="4">
+        <f>ROUND((G2-I2)/G2*100,0)</f>
         <v>18</v>
       </c>
-      <c r="I2" s="3" t="n">
+      <c r="I2" s="3">
         <v>4500</v>
       </c>
-      <c r="J2" s="5" t="n">
+      <c r="J2" s="5">
         <v>5</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
@@ -451,24 +744,24 @@
       <c r="F3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" s="3">
         <v>7500</v>
       </c>
-      <c r="H3" s="4" t="n">
-        <f aca="false">ROUND((G3-I3)/G3*100,0)</f>
+      <c r="H3" s="4">
+        <f>ROUND((G3-I3)/G3*100,0)</f>
         <v>13</v>
       </c>
-      <c r="I3" s="3" t="n">
+      <c r="I3" s="3">
         <v>6500</v>
       </c>
-      <c r="J3" s="5" t="n">
+      <c r="J3" s="5">
         <v>10</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>24</v>
       </c>
@@ -487,24 +780,24 @@
       <c r="F4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G4" s="3">
         <v>4500</v>
       </c>
-      <c r="H4" s="4" t="n">
-        <f aca="false">ROUND((G4-I4)/G4*100,0)</f>
+      <c r="H4" s="4">
+        <f>ROUND((G4-I4)/G4*100,0)</f>
         <v>22</v>
       </c>
-      <c r="I4" s="3" t="n">
+      <c r="I4" s="3">
         <v>3500</v>
       </c>
-      <c r="J4" s="5" t="n">
+      <c r="J4" s="5">
         <v>10</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>30</v>
       </c>
@@ -523,17 +816,17 @@
       <c r="F5" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" s="3">
         <v>2000</v>
       </c>
-      <c r="H5" s="4" t="n">
-        <f aca="false">ROUND((G5-I5)/G5*100,0)</f>
+      <c r="H5" s="4">
+        <f>ROUND((G5-I5)/G5*100,0)</f>
         <v>25</v>
       </c>
-      <c r="I5" s="3" t="n">
+      <c r="I5" s="3">
         <v>1500</v>
       </c>
-      <c r="J5" s="5" t="n">
+      <c r="J5" s="5">
         <v>20</v>
       </c>
       <c r="K5" s="2" t="s">
@@ -541,12 +834,7 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>